--- a/Business-plan.xlsx
+++ b/Business-plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6df868eea3d0d45/Documents/A5/Entrepreneuriat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{7502C396-0C56-4FE3-B978-2D863F60562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26F0654B-F443-4805-86AF-AF666FDF9FFC}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{7502C396-0C56-4FE3-B978-2D863F60562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A3950DB-95D6-4BAB-BB74-6FBE94988345}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="smvIEcgixjVkYZe47Ye2wEZh571m4EnLpkIdzKh0qi8KwDsToY/cwMS+Dxxzh0O8AiZsgF12tz+33Q9jaz0xmA==" workbookSaltValue="AuC8gSw+MjkqjFr1bT9rDw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -22,7 +22,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Plan financier à imprimer'!$A$1:$CG$49</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="312">
   <si>
     <t>Saisissez toutes vos données dans les cellules bleues, le business plan apparaitra dans l'onglet suivant.</t>
   </si>
@@ -1312,6 +1311,15 @@
   </si>
   <si>
     <t>Compétences extérieures externalisées</t>
+  </si>
+  <si>
+    <t>06 85 67 01 99</t>
+  </si>
+  <si>
+    <t>mathilde.noel2a@orange.fr</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
   </si>
 </sst>
 </file>
@@ -3153,34 +3161,58 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3209,119 +3241,95 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3894,10 +3902,10 @@
     <row r="4" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="249"/>
       <c r="G4" s="232"/>
-      <c r="H4" s="286" t="s">
+      <c r="H4" s="291" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="286"/>
+      <c r="I4" s="291"/>
       <c r="J4" t="s">
         <v>6</v>
       </c>
@@ -3913,8 +3921,8 @@
     </row>
     <row r="5" spans="1:14" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G5" s="232"/>
-      <c r="H5" s="286"/>
-      <c r="I5" s="286"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
       <c r="J5" t="s">
         <v>10</v>
       </c>
@@ -3926,15 +3934,15 @@
       <c r="A6" s="275" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="288" t="s">
+      <c r="B6" s="289" t="s">
         <v>306</v>
       </c>
-      <c r="C6" s="288"/>
+      <c r="C6" s="289"/>
       <c r="G6" s="232"/>
-      <c r="H6" s="287" t="s">
+      <c r="H6" s="292" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="287"/>
+      <c r="I6" s="292"/>
       <c r="J6" t="s">
         <v>14</v>
       </c>
@@ -3943,16 +3951,16 @@
       <c r="A7" s="275" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="288" t="s">
+      <c r="B7" s="289" t="s">
         <v>302</v>
       </c>
-      <c r="C7" s="288"/>
+      <c r="C7" s="289"/>
       <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="232"/>
-      <c r="H7" s="287"/>
-      <c r="I7" s="287"/>
+      <c r="H7" s="292"/>
+      <c r="I7" s="292"/>
       <c r="J7" t="s">
         <v>17</v>
       </c>
@@ -3961,10 +3969,10 @@
       <c r="A8" s="275" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="288" t="s">
+      <c r="B8" s="289" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="288"/>
+      <c r="C8" s="289"/>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
@@ -3978,8 +3986,10 @@
       <c r="A9" s="275" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="289"/>
-      <c r="C9" s="289"/>
+      <c r="B9" s="293" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="293"/>
       <c r="G9" s="232"/>
       <c r="H9" s="232"/>
     </row>
@@ -3987,8 +3997,10 @@
       <c r="A10" s="275" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="290"/>
-      <c r="C10" s="290"/>
+      <c r="B10" s="286" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="286"/>
       <c r="G10" s="232"/>
       <c r="H10" s="232"/>
     </row>
@@ -3996,8 +4008,10 @@
       <c r="A11" s="275" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="288"/>
-      <c r="C11" s="288"/>
+      <c r="B11" s="289" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11" s="289"/>
       <c r="G11" s="232"/>
       <c r="H11" s="232"/>
       <c r="J11" t="s">
@@ -4009,8 +4023,8 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="293"/>
-      <c r="C12" s="293"/>
+      <c r="B12" s="290"/>
+      <c r="C12" s="290"/>
       <c r="G12" s="232"/>
       <c r="H12" s="232"/>
       <c r="J12" t="s">
@@ -4024,11 +4038,11 @@
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="292" t="s">
+      <c r="B13" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="292"/>
-      <c r="D13" s="292"/>
+      <c r="C13" s="288"/>
+      <c r="D13" s="288"/>
       <c r="E13" s="5" t="s">
         <v>19</v>
       </c>
@@ -6209,12 +6223,12 @@
       </c>
     </row>
     <row r="121" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="291" t="s">
+      <c r="A121" s="287" t="s">
         <v>145</v>
       </c>
-      <c r="B121" s="291"/>
-      <c r="C121" s="291"/>
-      <c r="D121" s="291"/>
+      <c r="B121" s="287"/>
+      <c r="C121" s="287"/>
+      <c r="D121" s="287"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3"/>
     <row r="123" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -6776,17 +6790,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="VoqSGVnJ/kVMWTwZHbiKc/FVx7jbnER/TRQDjola0On81ELD4h0E9cEcCL870mtIG1EMZP/ljKpfQX56ucqyuw==" saltValue="wTHf9jf/lYC8NYkYT4Mdog==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
+    <mergeCell ref="H4:I5"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="H4:I5"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="D151">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
@@ -6882,82 +6896,82 @@
       <c r="F2" s="24"/>
       <c r="G2" s="24"/>
       <c r="H2" s="25"/>
-      <c r="K2" s="294" t="s">
+      <c r="K2" s="302" t="s">
         <v>172</v>
       </c>
-      <c r="L2" s="295"/>
-      <c r="M2" s="295"/>
-      <c r="N2" s="295"/>
-      <c r="O2" s="295"/>
-      <c r="P2" s="295"/>
-      <c r="Q2" s="296"/>
-      <c r="T2" s="294" t="s">
+      <c r="L2" s="303"/>
+      <c r="M2" s="303"/>
+      <c r="N2" s="303"/>
+      <c r="O2" s="303"/>
+      <c r="P2" s="303"/>
+      <c r="Q2" s="304"/>
+      <c r="T2" s="302" t="s">
         <v>173</v>
       </c>
-      <c r="U2" s="295"/>
-      <c r="V2" s="295"/>
-      <c r="W2" s="295"/>
-      <c r="X2" s="295"/>
-      <c r="Y2" s="295"/>
-      <c r="Z2" s="296"/>
-      <c r="AC2" s="294" t="s">
+      <c r="U2" s="303"/>
+      <c r="V2" s="303"/>
+      <c r="W2" s="303"/>
+      <c r="X2" s="303"/>
+      <c r="Y2" s="303"/>
+      <c r="Z2" s="304"/>
+      <c r="AC2" s="302" t="s">
         <v>174</v>
       </c>
-      <c r="AD2" s="295"/>
-      <c r="AE2" s="295"/>
-      <c r="AF2" s="295"/>
-      <c r="AG2" s="295"/>
-      <c r="AH2" s="295"/>
-      <c r="AI2" s="296"/>
-      <c r="AL2" s="294" t="s">
+      <c r="AD2" s="303"/>
+      <c r="AE2" s="303"/>
+      <c r="AF2" s="303"/>
+      <c r="AG2" s="303"/>
+      <c r="AH2" s="303"/>
+      <c r="AI2" s="304"/>
+      <c r="AL2" s="302" t="s">
         <v>175</v>
       </c>
-      <c r="AM2" s="295"/>
-      <c r="AN2" s="295"/>
-      <c r="AO2" s="295"/>
-      <c r="AP2" s="295"/>
-      <c r="AQ2" s="295"/>
-      <c r="AR2" s="295"/>
-      <c r="AS2" s="295"/>
-      <c r="AT2" s="296"/>
-      <c r="AW2" s="294" t="s">
+      <c r="AM2" s="303"/>
+      <c r="AN2" s="303"/>
+      <c r="AO2" s="303"/>
+      <c r="AP2" s="303"/>
+      <c r="AQ2" s="303"/>
+      <c r="AR2" s="303"/>
+      <c r="AS2" s="303"/>
+      <c r="AT2" s="304"/>
+      <c r="AW2" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="AX2" s="295"/>
-      <c r="AY2" s="295"/>
-      <c r="AZ2" s="295"/>
-      <c r="BA2" s="295"/>
-      <c r="BB2" s="295"/>
-      <c r="BC2" s="296"/>
-      <c r="BF2" s="294" t="s">
+      <c r="AX2" s="303"/>
+      <c r="AY2" s="303"/>
+      <c r="AZ2" s="303"/>
+      <c r="BA2" s="303"/>
+      <c r="BB2" s="303"/>
+      <c r="BC2" s="304"/>
+      <c r="BF2" s="302" t="s">
         <v>177</v>
       </c>
-      <c r="BG2" s="295"/>
-      <c r="BH2" s="295"/>
-      <c r="BI2" s="295"/>
-      <c r="BJ2" s="295"/>
-      <c r="BK2" s="295"/>
-      <c r="BL2" s="296"/>
-      <c r="BO2" s="294" t="s">
+      <c r="BG2" s="303"/>
+      <c r="BH2" s="303"/>
+      <c r="BI2" s="303"/>
+      <c r="BJ2" s="303"/>
+      <c r="BK2" s="303"/>
+      <c r="BL2" s="304"/>
+      <c r="BO2" s="302" t="s">
         <v>178</v>
       </c>
-      <c r="BP2" s="295"/>
-      <c r="BQ2" s="295"/>
-      <c r="BR2" s="295"/>
-      <c r="BS2" s="295"/>
-      <c r="BT2" s="295"/>
-      <c r="BU2" s="295"/>
-      <c r="BV2" s="296"/>
-      <c r="BY2" s="294" t="s">
+      <c r="BP2" s="303"/>
+      <c r="BQ2" s="303"/>
+      <c r="BR2" s="303"/>
+      <c r="BS2" s="303"/>
+      <c r="BT2" s="303"/>
+      <c r="BU2" s="303"/>
+      <c r="BV2" s="304"/>
+      <c r="BY2" s="302" t="s">
         <v>179</v>
       </c>
-      <c r="BZ2" s="295"/>
-      <c r="CA2" s="295"/>
-      <c r="CB2" s="295"/>
-      <c r="CC2" s="295"/>
-      <c r="CD2" s="295"/>
-      <c r="CE2" s="295"/>
-      <c r="CF2" s="296"/>
+      <c r="BZ2" s="303"/>
+      <c r="CA2" s="303"/>
+      <c r="CB2" s="303"/>
+      <c r="CC2" s="303"/>
+      <c r="CD2" s="303"/>
+      <c r="CE2" s="303"/>
+      <c r="CF2" s="304"/>
     </row>
     <row r="3" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="26"/>
@@ -6965,66 +6979,66 @@
       <c r="F3" s="221"/>
       <c r="G3" s="221"/>
       <c r="H3" s="27"/>
-      <c r="K3" s="297"/>
-      <c r="L3" s="298"/>
-      <c r="M3" s="298"/>
-      <c r="N3" s="298"/>
-      <c r="O3" s="298"/>
-      <c r="P3" s="298"/>
-      <c r="Q3" s="299"/>
-      <c r="T3" s="297"/>
-      <c r="U3" s="298"/>
-      <c r="V3" s="298"/>
-      <c r="W3" s="298"/>
-      <c r="X3" s="298"/>
-      <c r="Y3" s="298"/>
-      <c r="Z3" s="299"/>
-      <c r="AC3" s="297"/>
-      <c r="AD3" s="298"/>
-      <c r="AE3" s="298"/>
-      <c r="AF3" s="298"/>
-      <c r="AG3" s="298"/>
-      <c r="AH3" s="298"/>
-      <c r="AI3" s="299"/>
-      <c r="AL3" s="297"/>
-      <c r="AM3" s="298"/>
-      <c r="AN3" s="298"/>
-      <c r="AO3" s="298"/>
-      <c r="AP3" s="298"/>
-      <c r="AQ3" s="298"/>
-      <c r="AR3" s="298"/>
-      <c r="AS3" s="298"/>
-      <c r="AT3" s="299"/>
-      <c r="AW3" s="297"/>
-      <c r="AX3" s="298"/>
-      <c r="AY3" s="298"/>
-      <c r="AZ3" s="298"/>
-      <c r="BA3" s="298"/>
-      <c r="BB3" s="298"/>
-      <c r="BC3" s="299"/>
-      <c r="BF3" s="297"/>
-      <c r="BG3" s="298"/>
-      <c r="BH3" s="298"/>
-      <c r="BI3" s="298"/>
-      <c r="BJ3" s="298"/>
-      <c r="BK3" s="298"/>
-      <c r="BL3" s="299"/>
-      <c r="BO3" s="297"/>
-      <c r="BP3" s="298"/>
-      <c r="BQ3" s="298"/>
-      <c r="BR3" s="298"/>
-      <c r="BS3" s="298"/>
-      <c r="BT3" s="298"/>
-      <c r="BU3" s="298"/>
-      <c r="BV3" s="299"/>
-      <c r="BY3" s="297"/>
-      <c r="BZ3" s="298"/>
-      <c r="CA3" s="298"/>
-      <c r="CB3" s="298"/>
-      <c r="CC3" s="298"/>
-      <c r="CD3" s="298"/>
-      <c r="CE3" s="298"/>
-      <c r="CF3" s="299"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="306"/>
+      <c r="M3" s="306"/>
+      <c r="N3" s="306"/>
+      <c r="O3" s="306"/>
+      <c r="P3" s="306"/>
+      <c r="Q3" s="307"/>
+      <c r="T3" s="305"/>
+      <c r="U3" s="306"/>
+      <c r="V3" s="306"/>
+      <c r="W3" s="306"/>
+      <c r="X3" s="306"/>
+      <c r="Y3" s="306"/>
+      <c r="Z3" s="307"/>
+      <c r="AC3" s="305"/>
+      <c r="AD3" s="306"/>
+      <c r="AE3" s="306"/>
+      <c r="AF3" s="306"/>
+      <c r="AG3" s="306"/>
+      <c r="AH3" s="306"/>
+      <c r="AI3" s="307"/>
+      <c r="AL3" s="305"/>
+      <c r="AM3" s="306"/>
+      <c r="AN3" s="306"/>
+      <c r="AO3" s="306"/>
+      <c r="AP3" s="306"/>
+      <c r="AQ3" s="306"/>
+      <c r="AR3" s="306"/>
+      <c r="AS3" s="306"/>
+      <c r="AT3" s="307"/>
+      <c r="AW3" s="305"/>
+      <c r="AX3" s="306"/>
+      <c r="AY3" s="306"/>
+      <c r="AZ3" s="306"/>
+      <c r="BA3" s="306"/>
+      <c r="BB3" s="306"/>
+      <c r="BC3" s="307"/>
+      <c r="BF3" s="305"/>
+      <c r="BG3" s="306"/>
+      <c r="BH3" s="306"/>
+      <c r="BI3" s="306"/>
+      <c r="BJ3" s="306"/>
+      <c r="BK3" s="306"/>
+      <c r="BL3" s="307"/>
+      <c r="BO3" s="305"/>
+      <c r="BP3" s="306"/>
+      <c r="BQ3" s="306"/>
+      <c r="BR3" s="306"/>
+      <c r="BS3" s="306"/>
+      <c r="BT3" s="306"/>
+      <c r="BU3" s="306"/>
+      <c r="BV3" s="307"/>
+      <c r="BY3" s="305"/>
+      <c r="BZ3" s="306"/>
+      <c r="CA3" s="306"/>
+      <c r="CB3" s="306"/>
+      <c r="CC3" s="306"/>
+      <c r="CD3" s="306"/>
+      <c r="CE3" s="306"/>
+      <c r="CF3" s="307"/>
     </row>
     <row r="4" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="26"/>
@@ -7032,66 +7046,66 @@
       <c r="F4" s="221"/>
       <c r="G4" s="221"/>
       <c r="H4" s="27"/>
-      <c r="K4" s="300"/>
-      <c r="L4" s="301"/>
-      <c r="M4" s="301"/>
-      <c r="N4" s="301"/>
-      <c r="O4" s="301"/>
-      <c r="P4" s="301"/>
-      <c r="Q4" s="302"/>
-      <c r="T4" s="300"/>
-      <c r="U4" s="301"/>
-      <c r="V4" s="301"/>
-      <c r="W4" s="301"/>
-      <c r="X4" s="301"/>
-      <c r="Y4" s="301"/>
-      <c r="Z4" s="302"/>
-      <c r="AC4" s="300"/>
-      <c r="AD4" s="301"/>
-      <c r="AE4" s="301"/>
-      <c r="AF4" s="301"/>
-      <c r="AG4" s="301"/>
-      <c r="AH4" s="301"/>
-      <c r="AI4" s="302"/>
-      <c r="AL4" s="300"/>
-      <c r="AM4" s="301"/>
-      <c r="AN4" s="301"/>
-      <c r="AO4" s="301"/>
-      <c r="AP4" s="301"/>
-      <c r="AQ4" s="301"/>
-      <c r="AR4" s="301"/>
-      <c r="AS4" s="301"/>
-      <c r="AT4" s="302"/>
-      <c r="AW4" s="300"/>
-      <c r="AX4" s="301"/>
-      <c r="AY4" s="301"/>
-      <c r="AZ4" s="301"/>
-      <c r="BA4" s="301"/>
-      <c r="BB4" s="301"/>
-      <c r="BC4" s="302"/>
-      <c r="BF4" s="300"/>
-      <c r="BG4" s="301"/>
-      <c r="BH4" s="301"/>
-      <c r="BI4" s="301"/>
-      <c r="BJ4" s="301"/>
-      <c r="BK4" s="301"/>
-      <c r="BL4" s="302"/>
-      <c r="BO4" s="300"/>
-      <c r="BP4" s="301"/>
-      <c r="BQ4" s="301"/>
-      <c r="BR4" s="301"/>
-      <c r="BS4" s="301"/>
-      <c r="BT4" s="301"/>
-      <c r="BU4" s="301"/>
-      <c r="BV4" s="302"/>
-      <c r="BY4" s="300"/>
-      <c r="BZ4" s="301"/>
-      <c r="CA4" s="301"/>
-      <c r="CB4" s="301"/>
-      <c r="CC4" s="301"/>
-      <c r="CD4" s="301"/>
-      <c r="CE4" s="301"/>
-      <c r="CF4" s="302"/>
+      <c r="K4" s="308"/>
+      <c r="L4" s="309"/>
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="309"/>
+      <c r="P4" s="309"/>
+      <c r="Q4" s="310"/>
+      <c r="T4" s="308"/>
+      <c r="U4" s="309"/>
+      <c r="V4" s="309"/>
+      <c r="W4" s="309"/>
+      <c r="X4" s="309"/>
+      <c r="Y4" s="309"/>
+      <c r="Z4" s="310"/>
+      <c r="AC4" s="308"/>
+      <c r="AD4" s="309"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="309"/>
+      <c r="AG4" s="309"/>
+      <c r="AH4" s="309"/>
+      <c r="AI4" s="310"/>
+      <c r="AL4" s="308"/>
+      <c r="AM4" s="309"/>
+      <c r="AN4" s="309"/>
+      <c r="AO4" s="309"/>
+      <c r="AP4" s="309"/>
+      <c r="AQ4" s="309"/>
+      <c r="AR4" s="309"/>
+      <c r="AS4" s="309"/>
+      <c r="AT4" s="310"/>
+      <c r="AW4" s="308"/>
+      <c r="AX4" s="309"/>
+      <c r="AY4" s="309"/>
+      <c r="AZ4" s="309"/>
+      <c r="BA4" s="309"/>
+      <c r="BB4" s="309"/>
+      <c r="BC4" s="310"/>
+      <c r="BF4" s="308"/>
+      <c r="BG4" s="309"/>
+      <c r="BH4" s="309"/>
+      <c r="BI4" s="309"/>
+      <c r="BJ4" s="309"/>
+      <c r="BK4" s="309"/>
+      <c r="BL4" s="310"/>
+      <c r="BO4" s="308"/>
+      <c r="BP4" s="309"/>
+      <c r="BQ4" s="309"/>
+      <c r="BR4" s="309"/>
+      <c r="BS4" s="309"/>
+      <c r="BT4" s="309"/>
+      <c r="BU4" s="309"/>
+      <c r="BV4" s="310"/>
+      <c r="BY4" s="308"/>
+      <c r="BZ4" s="309"/>
+      <c r="CA4" s="309"/>
+      <c r="CB4" s="309"/>
+      <c r="CC4" s="309"/>
+      <c r="CD4" s="309"/>
+      <c r="CE4" s="309"/>
+      <c r="CF4" s="310"/>
     </row>
     <row r="5" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="26"/>
@@ -7102,11 +7116,11 @@
     </row>
     <row r="6" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
-      <c r="E6" s="333" t="s">
+      <c r="E6" s="325" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="333"/>
-      <c r="G6" s="333"/>
+      <c r="F6" s="325"/>
+      <c r="G6" s="325"/>
       <c r="H6" s="27"/>
       <c r="K6" s="1" t="s">
         <v>181</v>
@@ -7173,9 +7187,9 @@
     </row>
     <row r="7" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
-      <c r="E7" s="333"/>
-      <c r="F7" s="333"/>
-      <c r="G7" s="333"/>
+      <c r="E7" s="325"/>
+      <c r="F7" s="325"/>
+      <c r="G7" s="325"/>
       <c r="H7" s="27"/>
       <c r="K7" s="1" t="s">
         <v>183</v>
@@ -7245,26 +7259,26 @@
         <v>184</v>
       </c>
       <c r="T8" s="1"/>
-      <c r="AG8" s="315" t="s">
+      <c r="AG8" s="321" t="s">
         <v>65</v>
       </c>
-      <c r="AH8" s="305" t="s">
+      <c r="AH8" s="323" t="s">
         <v>66</v>
       </c>
-      <c r="AI8" s="317" t="s">
+      <c r="AI8" s="311" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:84" ht="15.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="327" t="s">
+      <c r="K9" s="315" t="s">
         <v>185</v>
       </c>
-      <c r="L9" s="328"/>
-      <c r="M9" s="328"/>
-      <c r="N9" s="328"/>
-      <c r="O9" s="328"/>
-      <c r="P9" s="328"/>
-      <c r="Q9" s="325" t="s">
+      <c r="L9" s="316"/>
+      <c r="M9" s="316"/>
+      <c r="N9" s="316"/>
+      <c r="O9" s="316"/>
+      <c r="P9" s="316"/>
+      <c r="Q9" s="313" t="s">
         <v>186</v>
       </c>
       <c r="U9" s="1" t="s">
@@ -7275,27 +7289,27 @@
         <v>SAS (IS)</v>
       </c>
       <c r="AC9" s="50"/>
-      <c r="AG9" s="316"/>
-      <c r="AH9" s="306"/>
-      <c r="AI9" s="324"/>
-      <c r="BA9" s="303" t="s">
+      <c r="AG9" s="322"/>
+      <c r="AH9" s="324"/>
+      <c r="AI9" s="312"/>
+      <c r="BA9" s="334" t="s">
         <v>65</v>
       </c>
-      <c r="BB9" s="305" t="s">
+      <c r="BB9" s="323" t="s">
         <v>66</v>
       </c>
-      <c r="BC9" s="307" t="s">
+      <c r="BC9" s="336" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K10" s="330"/>
-      <c r="L10" s="331"/>
-      <c r="M10" s="331"/>
-      <c r="N10" s="331"/>
-      <c r="O10" s="331"/>
-      <c r="P10" s="331"/>
-      <c r="Q10" s="326"/>
+      <c r="K10" s="318"/>
+      <c r="L10" s="319"/>
+      <c r="M10" s="319"/>
+      <c r="N10" s="319"/>
+      <c r="O10" s="319"/>
+      <c r="P10" s="319"/>
+      <c r="Q10" s="314"/>
       <c r="U10" s="1" t="s">
         <v>188</v>
       </c>
@@ -7322,9 +7336,9 @@
         <v>3657000</v>
       </c>
       <c r="AW10" s="50"/>
-      <c r="BA10" s="304"/>
-      <c r="BB10" s="306"/>
-      <c r="BC10" s="308"/>
+      <c r="BA10" s="335"/>
+      <c r="BB10" s="324"/>
+      <c r="BC10" s="337"/>
     </row>
     <row r="11" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K11" s="33"/>
@@ -7356,22 +7370,22 @@
         <f>AH11+AH11*'Données à saisir'!D118</f>
         <v>3657000</v>
       </c>
-      <c r="AO11" s="315" t="s">
+      <c r="AO11" s="321" t="s">
         <v>65</v>
       </c>
-      <c r="AP11" s="305" t="s">
+      <c r="AP11" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="AQ11" s="305" t="s">
+      <c r="AQ11" s="323" t="s">
         <v>66</v>
       </c>
-      <c r="AR11" s="305" t="s">
+      <c r="AR11" s="323" t="s">
         <v>192</v>
       </c>
-      <c r="AS11" s="305" t="s">
+      <c r="AS11" s="323" t="s">
         <v>67</v>
       </c>
-      <c r="AT11" s="317" t="s">
+      <c r="AT11" s="311" t="s">
         <v>192</v>
       </c>
       <c r="AW11" s="51" t="s">
@@ -7427,12 +7441,12 @@
         <v>0</v>
       </c>
       <c r="AL12" s="50"/>
-      <c r="AO12" s="319"/>
-      <c r="AP12" s="306"/>
-      <c r="AQ12" s="320"/>
-      <c r="AR12" s="306"/>
-      <c r="AS12" s="320"/>
-      <c r="AT12" s="318"/>
+      <c r="AO12" s="329"/>
+      <c r="AP12" s="324"/>
+      <c r="AQ12" s="330"/>
+      <c r="AR12" s="324"/>
+      <c r="AS12" s="330"/>
+      <c r="AT12" s="328"/>
       <c r="AW12" s="123" t="s">
         <v>197</v>
       </c>
@@ -7448,13 +7462,13 @@
         <f>AS15</f>
         <v>2484000.0000000005</v>
       </c>
-      <c r="BJ12" s="303" t="s">
+      <c r="BJ12" s="334" t="s">
         <v>65</v>
       </c>
-      <c r="BK12" s="305" t="s">
+      <c r="BK12" s="323" t="s">
         <v>66</v>
       </c>
-      <c r="BL12" s="307" t="s">
+      <c r="BL12" s="336" t="s">
         <v>67</v>
       </c>
     </row>
@@ -7535,59 +7549,59 @@
         <v>2484000.0000000005</v>
       </c>
       <c r="BF13" s="50"/>
-      <c r="BJ13" s="304"/>
-      <c r="BK13" s="306"/>
-      <c r="BL13" s="308"/>
-      <c r="BR13" s="303" t="s">
+      <c r="BJ13" s="335"/>
+      <c r="BK13" s="324"/>
+      <c r="BL13" s="337"/>
+      <c r="BR13" s="334" t="s">
         <v>128</v>
       </c>
-      <c r="BS13" s="305" t="s">
+      <c r="BS13" s="323" t="s">
         <v>129</v>
       </c>
-      <c r="BT13" s="305" t="s">
+      <c r="BT13" s="323" t="s">
         <v>130</v>
       </c>
-      <c r="BU13" s="305" t="s">
+      <c r="BU13" s="323" t="s">
         <v>131</v>
       </c>
-      <c r="BV13" s="307" t="s">
+      <c r="BV13" s="336" t="s">
         <v>132</v>
       </c>
-      <c r="BY13" s="303" t="s">
+      <c r="BY13" s="334" t="s">
         <v>133</v>
       </c>
-      <c r="BZ13" s="305" t="s">
+      <c r="BZ13" s="323" t="s">
         <v>134</v>
       </c>
-      <c r="CA13" s="305" t="s">
+      <c r="CA13" s="323" t="s">
         <v>135</v>
       </c>
-      <c r="CB13" s="305" t="s">
+      <c r="CB13" s="323" t="s">
         <v>136</v>
       </c>
-      <c r="CC13" s="305" t="s">
+      <c r="CC13" s="323" t="s">
         <v>137</v>
       </c>
-      <c r="CD13" s="305" t="s">
+      <c r="CD13" s="323" t="s">
         <v>138</v>
       </c>
-      <c r="CE13" s="309" t="s">
+      <c r="CE13" s="331" t="s">
         <v>139</v>
       </c>
-      <c r="CF13" s="311" t="s">
+      <c r="CF13" s="339" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="321" t="s">
+      <c r="B14" s="299" t="s">
         <v>201</v>
       </c>
-      <c r="C14" s="322"/>
-      <c r="D14" s="322"/>
-      <c r="E14" s="322"/>
-      <c r="F14" s="322"/>
-      <c r="G14" s="322"/>
-      <c r="H14" s="323"/>
+      <c r="C14" s="300"/>
+      <c r="D14" s="300"/>
+      <c r="E14" s="300"/>
+      <c r="F14" s="300"/>
+      <c r="G14" s="300"/>
+      <c r="H14" s="301"/>
       <c r="K14" s="44" t="str">
         <f>'Données à saisir'!A18</f>
         <v>Frais d’ouverture de compteurs</v>
@@ -7667,28 +7681,28 @@
       <c r="BK14" s="60"/>
       <c r="BL14" s="61"/>
       <c r="BO14" s="50"/>
-      <c r="BR14" s="304"/>
-      <c r="BS14" s="306"/>
-      <c r="BT14" s="306"/>
-      <c r="BU14" s="306"/>
-      <c r="BV14" s="308"/>
-      <c r="BY14" s="304"/>
-      <c r="BZ14" s="306"/>
-      <c r="CA14" s="306"/>
-      <c r="CB14" s="306"/>
-      <c r="CC14" s="306"/>
-      <c r="CD14" s="306"/>
-      <c r="CE14" s="310"/>
-      <c r="CF14" s="312"/>
+      <c r="BR14" s="335"/>
+      <c r="BS14" s="324"/>
+      <c r="BT14" s="324"/>
+      <c r="BU14" s="324"/>
+      <c r="BV14" s="337"/>
+      <c r="BY14" s="335"/>
+      <c r="BZ14" s="324"/>
+      <c r="CA14" s="324"/>
+      <c r="CB14" s="324"/>
+      <c r="CC14" s="324"/>
+      <c r="CD14" s="324"/>
+      <c r="CE14" s="332"/>
+      <c r="CF14" s="340"/>
     </row>
     <row r="15" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="321"/>
-      <c r="C15" s="322"/>
-      <c r="D15" s="322"/>
-      <c r="E15" s="322"/>
-      <c r="F15" s="322"/>
-      <c r="G15" s="322"/>
-      <c r="H15" s="323"/>
+      <c r="B15" s="299"/>
+      <c r="C15" s="300"/>
+      <c r="D15" s="300"/>
+      <c r="E15" s="300"/>
+      <c r="F15" s="300"/>
+      <c r="G15" s="300"/>
+      <c r="H15" s="301"/>
       <c r="K15" s="44" t="str">
         <f>'Données à saisir'!A19</f>
         <v>Logiciels, formations</v>
@@ -7799,13 +7813,13 @@
       </c>
     </row>
     <row r="16" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="321"/>
-      <c r="C16" s="322"/>
-      <c r="D16" s="322"/>
-      <c r="E16" s="322"/>
-      <c r="F16" s="322"/>
-      <c r="G16" s="322"/>
-      <c r="H16" s="323"/>
+      <c r="B16" s="299"/>
+      <c r="C16" s="300"/>
+      <c r="D16" s="300"/>
+      <c r="E16" s="300"/>
+      <c r="F16" s="300"/>
+      <c r="G16" s="300"/>
+      <c r="H16" s="301"/>
       <c r="K16" s="44" t="str">
         <f>'Données à saisir'!A20</f>
         <v>Dépôt marque, brevet, modèle</v>
@@ -7928,13 +7942,13 @@
       </c>
     </row>
     <row r="17" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="321"/>
-      <c r="C17" s="322"/>
-      <c r="D17" s="322"/>
-      <c r="E17" s="322"/>
-      <c r="F17" s="322"/>
-      <c r="G17" s="322"/>
-      <c r="H17" s="323"/>
+      <c r="B17" s="299"/>
+      <c r="C17" s="300"/>
+      <c r="D17" s="300"/>
+      <c r="E17" s="300"/>
+      <c r="F17" s="300"/>
+      <c r="G17" s="300"/>
+      <c r="H17" s="301"/>
       <c r="K17" s="44" t="str">
         <f>'Données à saisir'!A21</f>
         <v>Droits d’entrée</v>
@@ -8057,13 +8071,13 @@
       </c>
     </row>
     <row r="18" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="321"/>
-      <c r="C18" s="322"/>
-      <c r="D18" s="322"/>
-      <c r="E18" s="322"/>
-      <c r="F18" s="322"/>
-      <c r="G18" s="322"/>
-      <c r="H18" s="323"/>
+      <c r="B18" s="299"/>
+      <c r="C18" s="300"/>
+      <c r="D18" s="300"/>
+      <c r="E18" s="300"/>
+      <c r="F18" s="300"/>
+      <c r="G18" s="300"/>
+      <c r="H18" s="301"/>
       <c r="K18" s="44" t="str">
         <f>'Données à saisir'!A22</f>
         <v>Achat fonds de commerce ou parts</v>
@@ -8178,13 +8192,13 @@
       </c>
     </row>
     <row r="19" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="321"/>
-      <c r="C19" s="322"/>
-      <c r="D19" s="322"/>
-      <c r="E19" s="322"/>
-      <c r="F19" s="322"/>
-      <c r="G19" s="322"/>
-      <c r="H19" s="323"/>
+      <c r="B19" s="299"/>
+      <c r="C19" s="300"/>
+      <c r="D19" s="300"/>
+      <c r="E19" s="300"/>
+      <c r="F19" s="300"/>
+      <c r="G19" s="300"/>
+      <c r="H19" s="301"/>
       <c r="K19" s="44" t="str">
         <f>'Données à saisir'!A23</f>
         <v>Droit au bail</v>
@@ -8342,13 +8356,13 @@
       </c>
     </row>
     <row r="20" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="321"/>
-      <c r="C20" s="322"/>
-      <c r="D20" s="322"/>
-      <c r="E20" s="322"/>
-      <c r="F20" s="322"/>
-      <c r="G20" s="322"/>
-      <c r="H20" s="323"/>
+      <c r="B20" s="299"/>
+      <c r="C20" s="300"/>
+      <c r="D20" s="300"/>
+      <c r="E20" s="300"/>
+      <c r="F20" s="300"/>
+      <c r="G20" s="300"/>
+      <c r="H20" s="301"/>
       <c r="K20" s="44" t="str">
         <f>'Données à saisir'!A24</f>
         <v>Caution ou dépôt de garantie</v>
@@ -8752,14 +8766,14 @@
     </row>
     <row r="23" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="26"/>
-      <c r="C23" s="334" t="str">
+      <c r="C23" s="326" t="str">
         <f>IF(ISBLANK('Données à saisir'!B6),"",('Données à saisir'!B6))</f>
         <v>NOEL MOUCHEUX Mathilde / LAPLACE JOUINOT Hugo</v>
       </c>
-      <c r="D23" s="334"/>
-      <c r="E23" s="334"/>
-      <c r="F23" s="334"/>
-      <c r="G23" s="334"/>
+      <c r="D23" s="326"/>
+      <c r="E23" s="326"/>
+      <c r="F23" s="326"/>
+      <c r="G23" s="326"/>
       <c r="H23" s="27"/>
       <c r="K23" s="38" t="s">
         <v>237</v>
@@ -8857,11 +8871,11 @@
     </row>
     <row r="24" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="26"/>
-      <c r="C24" s="334"/>
-      <c r="D24" s="334"/>
-      <c r="E24" s="334"/>
-      <c r="F24" s="334"/>
-      <c r="G24" s="334"/>
+      <c r="C24" s="326"/>
+      <c r="D24" s="326"/>
+      <c r="E24" s="326"/>
+      <c r="F24" s="326"/>
+      <c r="G24" s="326"/>
       <c r="H24" s="27"/>
       <c r="K24" s="44" t="str">
         <f>'Données à saisir'!A27</f>
@@ -8961,11 +8975,11 @@
     </row>
     <row r="25" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="26"/>
-      <c r="C25" s="334"/>
-      <c r="D25" s="334"/>
-      <c r="E25" s="334"/>
-      <c r="F25" s="334"/>
-      <c r="G25" s="334"/>
+      <c r="C25" s="326"/>
+      <c r="D25" s="326"/>
+      <c r="E25" s="326"/>
+      <c r="F25" s="326"/>
+      <c r="G25" s="326"/>
       <c r="H25" s="27"/>
       <c r="K25" s="44" t="str">
         <f>'Données à saisir'!A28</f>
@@ -8975,15 +8989,15 @@
         <f>IF(ISBLANK('Données à saisir'!B28),"",'Données à saisir'!B28)</f>
         <v>0</v>
       </c>
-      <c r="T25" s="294" t="s">
+      <c r="T25" s="302" t="s">
         <v>243</v>
       </c>
-      <c r="U25" s="295"/>
-      <c r="V25" s="295"/>
-      <c r="W25" s="295"/>
-      <c r="X25" s="295"/>
-      <c r="Y25" s="295"/>
-      <c r="Z25" s="296"/>
+      <c r="U25" s="303"/>
+      <c r="V25" s="303"/>
+      <c r="W25" s="303"/>
+      <c r="X25" s="303"/>
+      <c r="Y25" s="303"/>
+      <c r="Z25" s="304"/>
       <c r="AC25" s="44" t="str">
         <f>'Données à saisir'!A84</f>
         <v>Fournitures diverses</v>
@@ -9084,13 +9098,13 @@
         <f>IF(ISBLANK('Données à saisir'!B29),"",'Données à saisir'!B29)</f>
         <v>350000</v>
       </c>
-      <c r="T26" s="297"/>
-      <c r="U26" s="298"/>
-      <c r="V26" s="298"/>
-      <c r="W26" s="298"/>
-      <c r="X26" s="298"/>
-      <c r="Y26" s="298"/>
-      <c r="Z26" s="299"/>
+      <c r="T26" s="305"/>
+      <c r="U26" s="306"/>
+      <c r="V26" s="306"/>
+      <c r="W26" s="306"/>
+      <c r="X26" s="306"/>
+      <c r="Y26" s="306"/>
+      <c r="Z26" s="307"/>
       <c r="AC26" s="44" t="str">
         <f>'Données à saisir'!A85</f>
         <v>Entretien matériel et vêtements</v>
@@ -9226,13 +9240,13 @@
         <f>IF(ISBLANK('Données à saisir'!B30),"",'Données à saisir'!B30)</f>
         <v>750000</v>
       </c>
-      <c r="T27" s="300"/>
-      <c r="U27" s="301"/>
-      <c r="V27" s="301"/>
-      <c r="W27" s="301"/>
-      <c r="X27" s="301"/>
-      <c r="Y27" s="301"/>
-      <c r="Z27" s="302"/>
+      <c r="T27" s="308"/>
+      <c r="U27" s="309"/>
+      <c r="V27" s="309"/>
+      <c r="W27" s="309"/>
+      <c r="X27" s="309"/>
+      <c r="Y27" s="309"/>
+      <c r="Z27" s="310"/>
       <c r="AC27" s="44" t="str">
         <f>'Données à saisir'!A86</f>
         <v>Nettoyage des locaux</v>
@@ -9336,14 +9350,14 @@
     </row>
     <row r="28" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="26"/>
-      <c r="C28" s="335" t="str">
+      <c r="C28" s="327" t="str">
         <f>IF(ISBLANK('Données à saisir'!B7),"",('Données à saisir'!B7))</f>
         <v>WarmLunch</v>
       </c>
-      <c r="D28" s="335"/>
-      <c r="E28" s="335"/>
-      <c r="F28" s="335"/>
-      <c r="G28" s="335"/>
+      <c r="D28" s="327"/>
+      <c r="E28" s="327"/>
+      <c r="F28" s="327"/>
+      <c r="G28" s="327"/>
       <c r="H28" s="27"/>
       <c r="K28" s="44" t="str">
         <f>'Données à saisir'!A31</f>
@@ -9401,11 +9415,11 @@
       <c r="BF28" s="92" t="s">
         <v>253</v>
       </c>
-      <c r="BI28" s="314">
+      <c r="BI28" s="338">
         <f>Q31</f>
         <v>150000</v>
       </c>
-      <c r="BJ28" s="314"/>
+      <c r="BJ28" s="338"/>
       <c r="BO28" s="123" t="s">
         <v>217</v>
       </c>
@@ -9464,11 +9478,11 @@
     </row>
     <row r="29" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="26"/>
-      <c r="C29" s="335"/>
-      <c r="D29" s="335"/>
-      <c r="E29" s="335"/>
-      <c r="F29" s="335"/>
-      <c r="G29" s="335"/>
+      <c r="C29" s="327"/>
+      <c r="D29" s="327"/>
+      <c r="E29" s="327"/>
+      <c r="F29" s="327"/>
+      <c r="G29" s="327"/>
       <c r="H29" s="27"/>
       <c r="K29" s="39"/>
       <c r="Q29" s="42"/>
@@ -9508,15 +9522,15 @@
       <c r="AQ29" s="34"/>
       <c r="AR29" s="34"/>
       <c r="AS29" s="34"/>
-      <c r="AW29" s="294" t="s">
+      <c r="AW29" s="302" t="s">
         <v>254</v>
       </c>
-      <c r="AX29" s="295"/>
-      <c r="AY29" s="295"/>
-      <c r="AZ29" s="295"/>
-      <c r="BA29" s="295"/>
-      <c r="BB29" s="295"/>
-      <c r="BC29" s="296"/>
+      <c r="AX29" s="303"/>
+      <c r="AY29" s="303"/>
+      <c r="AZ29" s="303"/>
+      <c r="BA29" s="303"/>
+      <c r="BB29" s="303"/>
+      <c r="BC29" s="304"/>
       <c r="BF29" s="161"/>
       <c r="BG29" s="161"/>
       <c r="BI29" s="172"/>
@@ -9582,11 +9596,11 @@
     </row>
     <row r="30" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="26"/>
-      <c r="C30" s="335"/>
-      <c r="D30" s="335"/>
-      <c r="E30" s="335"/>
-      <c r="F30" s="335"/>
-      <c r="G30" s="335"/>
+      <c r="C30" s="327"/>
+      <c r="D30" s="327"/>
+      <c r="E30" s="327"/>
+      <c r="F30" s="327"/>
+      <c r="G30" s="327"/>
       <c r="H30" s="27"/>
       <c r="K30" s="38" t="str">
         <f>'Données à saisir'!A32</f>
@@ -9634,13 +9648,13 @@
       <c r="AR30" s="99"/>
       <c r="AS30" s="99"/>
       <c r="AT30" s="99"/>
-      <c r="AW30" s="297"/>
-      <c r="AX30" s="298"/>
-      <c r="AY30" s="298"/>
-      <c r="AZ30" s="298"/>
-      <c r="BA30" s="298"/>
-      <c r="BB30" s="298"/>
-      <c r="BC30" s="299"/>
+      <c r="AW30" s="305"/>
+      <c r="AX30" s="306"/>
+      <c r="AY30" s="306"/>
+      <c r="AZ30" s="306"/>
+      <c r="BA30" s="306"/>
+      <c r="BB30" s="306"/>
+      <c r="BC30" s="307"/>
       <c r="BF30" s="1"/>
       <c r="BJ30" s="50"/>
       <c r="BK30" s="191"/>
@@ -9706,11 +9720,11 @@
     </row>
     <row r="31" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="26"/>
-      <c r="C31" s="335"/>
-      <c r="D31" s="335"/>
-      <c r="E31" s="335"/>
-      <c r="F31" s="335"/>
-      <c r="G31" s="335"/>
+      <c r="C31" s="327"/>
+      <c r="D31" s="327"/>
+      <c r="E31" s="327"/>
+      <c r="F31" s="327"/>
+      <c r="G31" s="327"/>
       <c r="H31" s="27"/>
       <c r="K31" s="38" t="str">
         <f>'Données à saisir'!A33</f>
@@ -9766,13 +9780,13 @@
       <c r="AR31" s="99"/>
       <c r="AS31" s="99"/>
       <c r="AT31" s="99"/>
-      <c r="AW31" s="300"/>
-      <c r="AX31" s="301"/>
-      <c r="AY31" s="301"/>
-      <c r="AZ31" s="301"/>
-      <c r="BA31" s="301"/>
-      <c r="BB31" s="301"/>
-      <c r="BC31" s="302"/>
+      <c r="AW31" s="308"/>
+      <c r="AX31" s="309"/>
+      <c r="AY31" s="309"/>
+      <c r="AZ31" s="309"/>
+      <c r="BA31" s="309"/>
+      <c r="BB31" s="309"/>
+      <c r="BC31" s="310"/>
       <c r="BF31" s="180"/>
       <c r="BI31" s="169"/>
       <c r="BJ31" s="181"/>
@@ -9837,11 +9851,11 @@
     </row>
     <row r="32" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="26"/>
-      <c r="C32" s="335"/>
-      <c r="D32" s="335"/>
-      <c r="E32" s="335"/>
-      <c r="F32" s="335"/>
-      <c r="G32" s="335"/>
+      <c r="C32" s="327"/>
+      <c r="D32" s="327"/>
+      <c r="E32" s="327"/>
+      <c r="F32" s="327"/>
+      <c r="G32" s="327"/>
       <c r="H32" s="27"/>
       <c r="K32" s="39"/>
       <c r="O32" s="1" t="s">
@@ -9937,14 +9951,14 @@
     </row>
     <row r="33" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="26"/>
-      <c r="C33" s="338" t="str">
+      <c r="C33" s="296" t="str">
         <f>IF(ISBLANK('Données à saisir'!B8),"",('Données à saisir'!B8))</f>
         <v>SAS (IS)</v>
       </c>
-      <c r="D33" s="338"/>
-      <c r="E33" s="338"/>
-      <c r="F33" s="338"/>
-      <c r="G33" s="338"/>
+      <c r="D33" s="296"/>
+      <c r="E33" s="296"/>
+      <c r="F33" s="296"/>
+      <c r="G33" s="296"/>
       <c r="H33" s="27"/>
       <c r="K33" s="35"/>
       <c r="Q33" s="43"/>
@@ -10047,21 +10061,21 @@
     </row>
     <row r="34" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="26"/>
-      <c r="C34" s="338"/>
-      <c r="D34" s="338"/>
-      <c r="E34" s="338"/>
-      <c r="F34" s="338"/>
-      <c r="G34" s="338"/>
+      <c r="C34" s="296"/>
+      <c r="D34" s="296"/>
+      <c r="E34" s="296"/>
+      <c r="F34" s="296"/>
+      <c r="G34" s="296"/>
       <c r="H34" s="27"/>
-      <c r="K34" s="327" t="s">
+      <c r="K34" s="315" t="s">
         <v>258</v>
       </c>
-      <c r="L34" s="328"/>
-      <c r="M34" s="328"/>
-      <c r="N34" s="328"/>
-      <c r="O34" s="328"/>
-      <c r="P34" s="329"/>
-      <c r="Q34" s="325" t="s">
+      <c r="L34" s="316"/>
+      <c r="M34" s="316"/>
+      <c r="N34" s="316"/>
+      <c r="O34" s="316"/>
+      <c r="P34" s="317"/>
+      <c r="Q34" s="313" t="s">
         <v>186</v>
       </c>
       <c r="T34" s="44" t="str">
@@ -10084,29 +10098,29 @@
       <c r="AG34" s="62"/>
       <c r="AH34" s="62"/>
       <c r="AI34" s="69"/>
-      <c r="AL34" s="294" t="s">
+      <c r="AL34" s="302" t="s">
         <v>252</v>
       </c>
-      <c r="AM34" s="295"/>
-      <c r="AN34" s="295"/>
-      <c r="AO34" s="295"/>
-      <c r="AP34" s="295"/>
-      <c r="AQ34" s="295"/>
-      <c r="AR34" s="295"/>
-      <c r="AS34" s="295"/>
-      <c r="AT34" s="296"/>
+      <c r="AM34" s="303"/>
+      <c r="AN34" s="303"/>
+      <c r="AO34" s="303"/>
+      <c r="AP34" s="303"/>
+      <c r="AQ34" s="303"/>
+      <c r="AR34" s="303"/>
+      <c r="AS34" s="303"/>
+      <c r="AT34" s="304"/>
       <c r="AW34" s="161"/>
       <c r="AX34" s="161"/>
       <c r="AZ34" s="172" t="s">
         <v>259</v>
       </c>
-      <c r="BA34" s="303" t="s">
+      <c r="BA34" s="334" t="s">
         <v>65</v>
       </c>
-      <c r="BB34" s="305" t="s">
+      <c r="BB34" s="323" t="s">
         <v>66</v>
       </c>
-      <c r="BC34" s="307" t="s">
+      <c r="BC34" s="336" t="s">
         <v>67</v>
       </c>
       <c r="BF34" s="183"/>
@@ -10175,19 +10189,19 @@
     </row>
     <row r="35" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="26"/>
-      <c r="C35" s="338"/>
-      <c r="D35" s="338"/>
-      <c r="E35" s="338"/>
-      <c r="F35" s="338"/>
-      <c r="G35" s="338"/>
+      <c r="C35" s="296"/>
+      <c r="D35" s="296"/>
+      <c r="E35" s="296"/>
+      <c r="F35" s="296"/>
+      <c r="G35" s="296"/>
       <c r="H35" s="27"/>
-      <c r="K35" s="330"/>
-      <c r="L35" s="331"/>
-      <c r="M35" s="331"/>
-      <c r="N35" s="331"/>
-      <c r="O35" s="331"/>
-      <c r="P35" s="332"/>
-      <c r="Q35" s="326"/>
+      <c r="K35" s="318"/>
+      <c r="L35" s="319"/>
+      <c r="M35" s="319"/>
+      <c r="N35" s="319"/>
+      <c r="O35" s="319"/>
+      <c r="P35" s="320"/>
+      <c r="Q35" s="314"/>
       <c r="T35" s="44" t="str">
         <f>K17</f>
         <v>Droits d’entrée</v>
@@ -10222,24 +10236,24 @@
         <f>AI16-AI17</f>
         <v>785861.07999999949</v>
       </c>
-      <c r="AL35" s="297"/>
-      <c r="AM35" s="298"/>
-      <c r="AN35" s="298"/>
-      <c r="AO35" s="298"/>
-      <c r="AP35" s="298"/>
-      <c r="AQ35" s="298"/>
-      <c r="AR35" s="298"/>
-      <c r="AS35" s="298"/>
-      <c r="AT35" s="299"/>
+      <c r="AL35" s="305"/>
+      <c r="AM35" s="306"/>
+      <c r="AN35" s="306"/>
+      <c r="AO35" s="306"/>
+      <c r="AP35" s="306"/>
+      <c r="AQ35" s="306"/>
+      <c r="AR35" s="306"/>
+      <c r="AS35" s="306"/>
+      <c r="AT35" s="307"/>
       <c r="AW35" s="63" t="s">
         <v>261</v>
       </c>
       <c r="AX35" s="64"/>
       <c r="AY35" s="64"/>
       <c r="AZ35" s="64"/>
-      <c r="BA35" s="304"/>
-      <c r="BB35" s="306"/>
-      <c r="BC35" s="308"/>
+      <c r="BA35" s="335"/>
+      <c r="BB35" s="324"/>
+      <c r="BC35" s="337"/>
       <c r="BO35" s="123" t="str">
         <f>AC42</f>
         <v>Frais bancaires, charges financières</v>
@@ -10340,15 +10354,15 @@
         <f>IF(ISBLANK('Données à saisir'!D91),0,'Données à saisir'!D91)</f>
         <v>6138.36</v>
       </c>
-      <c r="AL36" s="300"/>
-      <c r="AM36" s="301"/>
-      <c r="AN36" s="301"/>
-      <c r="AO36" s="301"/>
-      <c r="AP36" s="301"/>
-      <c r="AQ36" s="301"/>
-      <c r="AR36" s="301"/>
-      <c r="AS36" s="301"/>
-      <c r="AT36" s="302"/>
+      <c r="AL36" s="308"/>
+      <c r="AM36" s="309"/>
+      <c r="AN36" s="309"/>
+      <c r="AO36" s="309"/>
+      <c r="AP36" s="309"/>
+      <c r="AQ36" s="309"/>
+      <c r="AR36" s="309"/>
+      <c r="AS36" s="309"/>
+      <c r="AT36" s="310"/>
       <c r="AW36" s="123" t="s">
         <v>262</v>
       </c>
@@ -10815,15 +10829,15 @@
         <f>IF('Données à saisir'!C136="Oui",'Données à saisir'!I147,'Données à saisir'!D147)</f>
         <v>84000</v>
       </c>
-      <c r="AO40" s="315" t="s">
+      <c r="AO40" s="321" t="s">
         <v>65</v>
       </c>
       <c r="AP40" s="125"/>
-      <c r="AQ40" s="309" t="s">
+      <c r="AQ40" s="331" t="s">
         <v>66</v>
       </c>
       <c r="AR40" s="134"/>
-      <c r="AS40" s="309" t="s">
+      <c r="AS40" s="331" t="s">
         <v>67</v>
       </c>
       <c r="AT40" s="83"/>
@@ -10929,11 +10943,11 @@
         <v>285825.66399999947</v>
       </c>
       <c r="AL41" s="50"/>
-      <c r="AO41" s="316"/>
+      <c r="AO41" s="322"/>
       <c r="AP41" s="126"/>
-      <c r="AQ41" s="310"/>
+      <c r="AQ41" s="332"/>
       <c r="AR41" s="135"/>
-      <c r="AS41" s="310"/>
+      <c r="AS41" s="332"/>
       <c r="AT41" s="130"/>
       <c r="BO41" s="123"/>
       <c r="BR41" s="216" t="str">
@@ -10999,14 +11013,14 @@
     </row>
     <row r="42" spans="2:84" ht="15.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="26"/>
-      <c r="C42" s="339" t="str">
+      <c r="C42" s="297" t="str">
         <f>IF(ISBLANK('Données à saisir'!B9),"",('Données à saisir'!B9))</f>
-        <v/>
-      </c>
-      <c r="D42" s="339"/>
-      <c r="E42" s="339"/>
-      <c r="F42" s="339"/>
-      <c r="G42" s="339"/>
+        <v>06 85 67 01 99</v>
+      </c>
+      <c r="D42" s="297"/>
+      <c r="E42" s="297"/>
+      <c r="F42" s="297"/>
+      <c r="G42" s="297"/>
       <c r="H42" s="27"/>
       <c r="K42" s="44" t="str">
         <f>IF(ISBLANK('Données à saisir'!A62),"",'Données à saisir'!A62)</f>
@@ -11081,9 +11095,9 @@
       <c r="AW42" s="161"/>
       <c r="AX42" s="161"/>
       <c r="AZ42" s="172"/>
-      <c r="BA42" s="313"/>
-      <c r="BB42" s="313"/>
-      <c r="BC42" s="313"/>
+      <c r="BA42" s="333"/>
+      <c r="BB42" s="333"/>
+      <c r="BC42" s="333"/>
       <c r="BF42" s="161"/>
       <c r="BG42" s="161"/>
       <c r="BI42" s="172"/>
@@ -11109,14 +11123,14 @@
     </row>
     <row r="43" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="26"/>
-      <c r="C43" s="340" t="str">
+      <c r="C43" s="298" t="str">
         <f>IF(ISBLANK('Données à saisir'!B10),"",('Données à saisir'!B10))</f>
-        <v/>
-      </c>
-      <c r="D43" s="340"/>
-      <c r="E43" s="340"/>
-      <c r="F43" s="340"/>
-      <c r="G43" s="340"/>
+        <v>mathilde.noel2a@orange.fr</v>
+      </c>
+      <c r="D43" s="298"/>
+      <c r="E43" s="298"/>
+      <c r="F43" s="298"/>
+      <c r="G43" s="298"/>
       <c r="H43" s="27"/>
       <c r="K43" s="44" t="str">
         <f>IF(ISBLANK('Données à saisir'!A63),"",'Données à saisir'!A63)</f>
@@ -11189,9 +11203,9 @@
       </c>
       <c r="AT43" s="120"/>
       <c r="AW43" s="1"/>
-      <c r="BA43" s="313"/>
-      <c r="BB43" s="313"/>
-      <c r="BC43" s="313"/>
+      <c r="BA43" s="333"/>
+      <c r="BB43" s="333"/>
+      <c r="BC43" s="333"/>
       <c r="BF43" s="1"/>
       <c r="BJ43" s="50"/>
       <c r="BK43" s="50"/>
@@ -11208,14 +11222,14 @@
     </row>
     <row r="44" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="26"/>
-      <c r="C44" s="340" t="str">
+      <c r="C44" s="298" t="str">
         <f>IF(ISBLANK('Données à saisir'!B11),"",('Données à saisir'!B11))</f>
-        <v/>
-      </c>
-      <c r="D44" s="340"/>
-      <c r="E44" s="340"/>
-      <c r="F44" s="340"/>
-      <c r="G44" s="340"/>
+        <v>Bordeaux</v>
+      </c>
+      <c r="D44" s="298"/>
+      <c r="E44" s="298"/>
+      <c r="F44" s="298"/>
+      <c r="G44" s="298"/>
       <c r="H44" s="27"/>
       <c r="K44" s="38" t="str">
         <f>IF(ISBLANK('Données à saisir'!A64),"",'Données à saisir'!A64)</f>
@@ -11447,14 +11461,14 @@
     </row>
     <row r="47" spans="2:84" ht="15.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="26"/>
-      <c r="C47" s="336">
+      <c r="C47" s="294">
         <f ca="1">TODAY()</f>
-        <v>45951</v>
-      </c>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
-      <c r="G47" s="337"/>
+        <v>45952</v>
+      </c>
+      <c r="D47" s="295"/>
+      <c r="E47" s="295"/>
+      <c r="F47" s="295"/>
+      <c r="G47" s="295"/>
       <c r="H47" s="27"/>
       <c r="K47" s="35"/>
       <c r="Q47" s="48"/>
@@ -11657,11 +11671,48 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="O9Zds206+6RicuEcdkZGX49ZytjNl58wwXxCBkIB/ONshGzm6/el1Heclo5wnUS5lVNnVAsUPbN/Ne+36aykiw==" saltValue="/ZJh2aHIWGe8iFj06c/G5w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="62">
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C33:G35"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="BY2:CF4"/>
+    <mergeCell ref="BR13:BR14"/>
+    <mergeCell ref="BS13:BS14"/>
+    <mergeCell ref="BT13:BT14"/>
+    <mergeCell ref="BU13:BU14"/>
+    <mergeCell ref="BV13:BV14"/>
+    <mergeCell ref="BY13:BY14"/>
+    <mergeCell ref="BZ13:BZ14"/>
+    <mergeCell ref="CA13:CA14"/>
+    <mergeCell ref="CB13:CB14"/>
+    <mergeCell ref="CC13:CC14"/>
+    <mergeCell ref="CD13:CD14"/>
+    <mergeCell ref="CE13:CE14"/>
+    <mergeCell ref="CF13:CF14"/>
+    <mergeCell ref="BO2:BV4"/>
+    <mergeCell ref="BC42:BC43"/>
+    <mergeCell ref="BF2:BL4"/>
+    <mergeCell ref="BJ12:BJ13"/>
+    <mergeCell ref="BK12:BK13"/>
+    <mergeCell ref="BL12:BL13"/>
+    <mergeCell ref="AW2:BC4"/>
+    <mergeCell ref="AW29:BC31"/>
+    <mergeCell ref="BA9:BA10"/>
+    <mergeCell ref="BB9:BB10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BA34:BA35"/>
+    <mergeCell ref="BB34:BB35"/>
+    <mergeCell ref="BC34:BC35"/>
+    <mergeCell ref="BI28:BJ28"/>
+    <mergeCell ref="AS40:AS41"/>
+    <mergeCell ref="AQ40:AQ41"/>
+    <mergeCell ref="AO40:AO41"/>
+    <mergeCell ref="BA42:BA43"/>
+    <mergeCell ref="BB42:BB43"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AL2:AT4"/>
+    <mergeCell ref="AL34:AT36"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AR11:AR12"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AS11:AS12"/>
     <mergeCell ref="B14:H20"/>
     <mergeCell ref="T2:Z4"/>
     <mergeCell ref="AI8:AI9"/>
@@ -11677,48 +11728,11 @@
     <mergeCell ref="Q9:Q10"/>
     <mergeCell ref="C23:G25"/>
     <mergeCell ref="C28:G32"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AL2:AT4"/>
-    <mergeCell ref="AL34:AT36"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AR11:AR12"/>
-    <mergeCell ref="AO11:AO12"/>
-    <mergeCell ref="AQ11:AQ12"/>
-    <mergeCell ref="AS11:AS12"/>
-    <mergeCell ref="AS40:AS41"/>
-    <mergeCell ref="AQ40:AQ41"/>
-    <mergeCell ref="AO40:AO41"/>
-    <mergeCell ref="BA42:BA43"/>
-    <mergeCell ref="BB42:BB43"/>
-    <mergeCell ref="BC42:BC43"/>
-    <mergeCell ref="BF2:BL4"/>
-    <mergeCell ref="BJ12:BJ13"/>
-    <mergeCell ref="BK12:BK13"/>
-    <mergeCell ref="BL12:BL13"/>
-    <mergeCell ref="AW2:BC4"/>
-    <mergeCell ref="AW29:BC31"/>
-    <mergeCell ref="BA9:BA10"/>
-    <mergeCell ref="BB9:BB10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BA34:BA35"/>
-    <mergeCell ref="BB34:BB35"/>
-    <mergeCell ref="BC34:BC35"/>
-    <mergeCell ref="BI28:BJ28"/>
-    <mergeCell ref="BY2:CF4"/>
-    <mergeCell ref="BR13:BR14"/>
-    <mergeCell ref="BS13:BS14"/>
-    <mergeCell ref="BT13:BT14"/>
-    <mergeCell ref="BU13:BU14"/>
-    <mergeCell ref="BV13:BV14"/>
-    <mergeCell ref="BY13:BY14"/>
-    <mergeCell ref="BZ13:BZ14"/>
-    <mergeCell ref="CA13:CA14"/>
-    <mergeCell ref="CB13:CB14"/>
-    <mergeCell ref="CC13:CC14"/>
-    <mergeCell ref="CD13:CD14"/>
-    <mergeCell ref="CE13:CE14"/>
-    <mergeCell ref="CF13:CF14"/>
-    <mergeCell ref="BO2:BV4"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C33:G35"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C43:G43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11839,9 +11853,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11983,19 +12000,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E50BF3-B19B-4334-9283-491D6307CC84}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{457EDE14-9277-428C-9291-E2CD14632DF6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12019,9 +12032,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{457EDE14-9277-428C-9291-E2CD14632DF6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E50BF3-B19B-4334-9283-491D6307CC84}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>